--- a/docs/cwc/API 명세서.xlsx
+++ b/docs/cwc/API 명세서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KDT\git\mjc_b-hotel-reservation\docs\phi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\mjc_b-hotel-reservation\docs\cwc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EC98DE-EB3C-4A0F-B92B-9B23EF2676DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B0756-5769-48FC-A399-DDD18A65688B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2242" yWindow="322" windowWidth="16485" windowHeight="12136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9605" yWindow="5" windowWidth="19190" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="57">
   <si>
     <t>화면ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,6 +79,184 @@
   </si>
   <si>
     <t>회원가입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/room</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADMIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/room/image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"requestDto":{RoomDto}
+"files":이미지파일1
+"files":이미지파일2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomResponseWithImagesDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/room/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anonymous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/room/images/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실정보 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실+이미지 정보 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실+이미지들 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PATCH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomDto 변경할 멤버만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실정보 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실정보 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELETE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실정보+이미지들 삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R001,S002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/roomimage/room/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/roomimage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomImageDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지정보 추가(file upload 안함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomImageResponseDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>url주소(~~/roomId)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>url주소(~~/roomId),MultipartFile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실번호에 이미지파일 추가하면 이미지정보 추가됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/roomimage/image/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>url주소(~~/roomImageId),MultipartFile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옛날이미지파일 삭제하고, 새로운 이미지파일로 업로드하고 이미지정보 수정함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/roomimage/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지정보 조회, 이미지볼수 있는 url 포함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/roomimage/download/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/roomimage/image/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>url주소(~~/roomImageId)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteArrayResource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지를 보여주는 용도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지를 다운로드하는 용도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지파일 삭제하고 이미지정보도 삭제함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R001, R002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R001, R002, S002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,8 +300,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -401,17 +585,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.5625" customWidth="1"/>
-    <col min="3" max="3" width="15.5625" customWidth="1"/>
-    <col min="4" max="5" width="20.5625" customWidth="1"/>
-    <col min="6" max="6" width="15.5625" customWidth="1"/>
-    <col min="7" max="8" width="20.5625" customWidth="1"/>
+    <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="4" max="4" width="29.625" customWidth="1"/>
+    <col min="5" max="5" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="73.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -434,7 +621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -455,6 +642,305 @@
       </c>
       <c r="H2" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cwc/API 명세서.xlsx
+++ b/docs/cwc/API 명세서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\mjc_b-hotel-reservation\docs\cwc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\mjc_b-hotel-reservation\docs\cwc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B0756-5769-48FC-A399-DDD18A65688B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DE4549-C10D-4C11-8F5D-DCC44D12EE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9605" yWindow="5" windowWidth="19190" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t>화면ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,14 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>객실+이미지 정보 조회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>객실+이미지들 추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PATCH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,10 +148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>객실정보+이미지들 삭제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>R001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -257,6 +245,34 @@
   </si>
   <si>
     <t>R001, R002, S002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/v1/room/hotel/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>url주소(~~/hotelId)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호텔id 에 해당하는 객실들의  paging 정보, 10개당 1페이지, 층수 내림차순 방번호 오름차순</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Page&lt;RoomDto&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실, 모든 이미지정보들 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실과 이미지들 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객실정보와 이미지들 삭제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -585,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -594,7 +610,7 @@
     <col min="4" max="4" width="29.625" customWidth="1"/>
     <col min="5" max="5" width="31.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="73.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="86" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -646,7 +662,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -661,7 +677,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -669,7 +685,7 @@
     </row>
     <row r="4" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -684,7 +700,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -692,7 +708,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -701,7 +717,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -715,7 +731,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -724,13 +740,13 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -738,22 +754,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -761,186 +777,209 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" t="s">
-        <v>38</v>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
       </c>
       <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
         <v>15</v>
       </c>
-      <c r="G16" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" t="s">
-        <v>36</v>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cwc/API 명세서.xlsx
+++ b/docs/cwc/API 명세서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\mjc_b-hotel-reservation\docs\cwc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DE4549-C10D-4C11-8F5D-DCC44D12EE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3954771-C0EF-495D-8474-A783FB53D713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9605" yWindow="5" windowWidth="19190" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="65">
   <si>
     <t>화면ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -273,6 +273,22 @@
   </si>
   <si>
     <t>객실정보와 이미지들 삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행률</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최원철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍길동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -316,11 +332,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -601,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -614,7 +631,7 @@
     <col min="8" max="8" width="29.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -636,8 +653,14 @@
       <c r="H1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -659,8 +682,14 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>29</v>
       </c>
@@ -682,8 +711,14 @@
       <c r="H3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>29</v>
       </c>
@@ -705,8 +740,14 @@
       <c r="H4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>30</v>
       </c>
@@ -728,8 +769,14 @@
       <c r="H5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>30</v>
       </c>
@@ -751,8 +798,14 @@
       <c r="H6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -774,8 +827,14 @@
       <c r="H7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -797,8 +856,14 @@
       <c r="H8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>29</v>
       </c>
@@ -820,8 +885,14 @@
       <c r="H9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>52</v>
       </c>
@@ -843,8 +914,14 @@
       <c r="H11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>52</v>
       </c>
@@ -866,8 +943,14 @@
       <c r="H12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>52</v>
       </c>
@@ -889,8 +972,14 @@
       <c r="H13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>53</v>
       </c>
@@ -912,8 +1001,14 @@
       <c r="H14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>53</v>
       </c>
@@ -935,8 +1030,14 @@
       <c r="H15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>53</v>
       </c>
@@ -958,8 +1059,14 @@
       <c r="H16" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I16" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>52</v>
       </c>
@@ -980,6 +1087,12 @@
       </c>
       <c r="H17" t="s">
         <v>33</v>
+      </c>
+      <c r="I17" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
